--- a/mobile-automation/reports/Excel/Automation_Test_Report.xlsx
+++ b/mobile-automation/reports/Excel/Automation_Test_Report.xlsx
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>400</v>
+        <v>510</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>400</v>
+        <v>510</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>32</v>
+        <v>40.8</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:E511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9131,12 +9131,12 @@
       </c>
       <c r="B372" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C372" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #01</t>
+          <t>Android Appium Notifications Spec #11</t>
         </is>
       </c>
       <c r="D372" s="6" t="n">
@@ -9154,12 +9154,12 @@
       </c>
       <c r="B373" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C373" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #02</t>
+          <t>Android Appium Notifications Spec #12</t>
         </is>
       </c>
       <c r="D373" s="6" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="B374" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C374" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #03</t>
+          <t>Android Appium Notifications Spec #13</t>
         </is>
       </c>
       <c r="D374" s="6" t="n">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="B375" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C375" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #04</t>
+          <t>Android Appium Notifications Spec #14</t>
         </is>
       </c>
       <c r="D375" s="6" t="n">
@@ -9223,12 +9223,12 @@
       </c>
       <c r="B376" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C376" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #05</t>
+          <t>Android Appium Notifications Spec #15</t>
         </is>
       </c>
       <c r="D376" s="6" t="n">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="B377" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C377" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #06</t>
+          <t>Android Appium Notifications Spec #16</t>
         </is>
       </c>
       <c r="D377" s="6" t="n">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="B378" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C378" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #07</t>
+          <t>Android Appium Notifications Spec #17</t>
         </is>
       </c>
       <c r="D378" s="6" t="n">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="B379" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C379" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #08</t>
+          <t>Android Appium Notifications Spec #18</t>
         </is>
       </c>
       <c r="D379" s="6" t="n">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="B380" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C380" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #09</t>
+          <t>Android Appium Notifications Spec #19</t>
         </is>
       </c>
       <c r="D380" s="6" t="n">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="B381" s="5" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C381" s="5" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #10</t>
+          <t>Android Appium Notifications Spec #20</t>
         </is>
       </c>
       <c r="D381" s="6" t="n">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="B382" s="5" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C382" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Offline Handling Spec #01</t>
+          <t>Android Appium File Upload Spec #01</t>
         </is>
       </c>
       <c r="D382" s="6" t="n">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="B383" s="5" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C383" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Offline Handling Spec #02</t>
+          <t>Android Appium File Upload Spec #02</t>
         </is>
       </c>
       <c r="D383" s="6" t="n">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="B384" s="5" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C384" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Offline Handling Spec #03</t>
+          <t>Android Appium File Upload Spec #03</t>
         </is>
       </c>
       <c r="D384" s="6" t="n">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="B385" s="5" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C385" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Offline Handling Spec #04</t>
+          <t>Android Appium File Upload Spec #04</t>
         </is>
       </c>
       <c r="D385" s="6" t="n">
@@ -9453,12 +9453,12 @@
       </c>
       <c r="B386" s="5" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C386" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Accessibility Spec #01</t>
+          <t>Android Appium File Upload Spec #05</t>
         </is>
       </c>
       <c r="D386" s="6" t="n">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B387" s="5" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C387" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Accessibility Spec #02</t>
+          <t>Android Appium File Upload Spec #06</t>
         </is>
       </c>
       <c r="D387" s="6" t="n">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="B388" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C388" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #01</t>
+          <t>Android Appium File Upload Spec #07</t>
         </is>
       </c>
       <c r="D388" s="6" t="n">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="B389" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C389" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #02</t>
+          <t>Android Appium File Upload Spec #08</t>
         </is>
       </c>
       <c r="D389" s="6" t="n">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="B390" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C390" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #03</t>
+          <t>Android Appium File Upload Spec #09</t>
         </is>
       </c>
       <c r="D390" s="6" t="n">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="B391" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C391" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #04</t>
+          <t>Android Appium File Upload Spec #10</t>
         </is>
       </c>
       <c r="D391" s="6" t="n">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="B392" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C392" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #05</t>
+          <t>Android Appium File Upload Spec #11</t>
         </is>
       </c>
       <c r="D392" s="6" t="n">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="B393" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C393" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #06</t>
+          <t>Android Appium File Upload Spec #12</t>
         </is>
       </c>
       <c r="D393" s="6" t="n">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="B394" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C394" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #07</t>
+          <t>Android Appium File Upload Spec #13</t>
         </is>
       </c>
       <c r="D394" s="6" t="n">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="B395" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C395" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #08</t>
+          <t>Android Appium File Upload Spec #14</t>
         </is>
       </c>
       <c r="D395" s="6" t="n">
@@ -9683,12 +9683,12 @@
       </c>
       <c r="B396" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C396" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #09</t>
+          <t>Android Appium File Upload Spec #15</t>
         </is>
       </c>
       <c r="D396" s="6" t="n">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="B397" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C397" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #10</t>
+          <t>Android Appium File Upload Spec #16</t>
         </is>
       </c>
       <c r="D397" s="6" t="n">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="B398" s="5" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C398" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #11</t>
+          <t>Android Appium File Upload Spec #17</t>
         </is>
       </c>
       <c r="D398" s="6" t="n">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="B399" s="5" t="inlineStr">
         <is>
-          <t>Performance Smoke Tests</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C399" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Performance Smoke Tests Spec #01</t>
+          <t>Android Appium File Upload Spec #18</t>
         </is>
       </c>
       <c r="D399" s="6" t="n">
@@ -9775,12 +9775,12 @@
       </c>
       <c r="B400" s="5" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C400" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Regression Suite Spec #01</t>
+          <t>Android Appium File Upload Spec #19</t>
         </is>
       </c>
       <c r="D400" s="6" t="n">
@@ -9798,18 +9798,2548 @@
       </c>
       <c r="B401" s="5" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C401" s="5" t="inlineStr">
         <is>
-          <t>Android Appium Regression Suite Spec #02</t>
+          <t>Android Appium File Upload Spec #20</t>
         </is>
       </c>
       <c r="D401" s="6" t="n">
         <v>0.04</v>
       </c>
       <c r="E401" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="4" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C402" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #01</t>
+        </is>
+      </c>
+      <c r="D402" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E402" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="4" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C403" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #02</t>
+        </is>
+      </c>
+      <c r="D403" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E403" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="4" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C404" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #03</t>
+        </is>
+      </c>
+      <c r="D404" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E404" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C405" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #04</t>
+        </is>
+      </c>
+      <c r="D405" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E405" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="4" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C406" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #05</t>
+        </is>
+      </c>
+      <c r="D406" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E406" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="4" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C407" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #06</t>
+        </is>
+      </c>
+      <c r="D407" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E407" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="4" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C408" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #07</t>
+        </is>
+      </c>
+      <c r="D408" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E408" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C409" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #08</t>
+        </is>
+      </c>
+      <c r="D409" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E409" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="4" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C410" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #09</t>
+        </is>
+      </c>
+      <c r="D410" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E410" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="4" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" s="5" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C411" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #10</t>
+        </is>
+      </c>
+      <c r="D411" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E411" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="4" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C412" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #01</t>
+        </is>
+      </c>
+      <c r="D412" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E412" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="4" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C413" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #02</t>
+        </is>
+      </c>
+      <c r="D413" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E413" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="4" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C414" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #03</t>
+        </is>
+      </c>
+      <c r="D414" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E414" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="4" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C415" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #04</t>
+        </is>
+      </c>
+      <c r="D415" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E415" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="4" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C416" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #05</t>
+        </is>
+      </c>
+      <c r="D416" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E416" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C417" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #06</t>
+        </is>
+      </c>
+      <c r="D417" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E417" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="4" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C418" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #07</t>
+        </is>
+      </c>
+      <c r="D418" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E418" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="4" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C419" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #08</t>
+        </is>
+      </c>
+      <c r="D419" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E419" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="4" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C420" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #09</t>
+        </is>
+      </c>
+      <c r="D420" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E420" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C421" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #10</t>
+        </is>
+      </c>
+      <c r="D421" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E421" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="4" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C422" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #11</t>
+        </is>
+      </c>
+      <c r="D422" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E422" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="4" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C423" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #12</t>
+        </is>
+      </c>
+      <c r="D423" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E423" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="4" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C424" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #13</t>
+        </is>
+      </c>
+      <c r="D424" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E424" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="4" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C425" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #14</t>
+        </is>
+      </c>
+      <c r="D425" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E425" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C426" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #15</t>
+        </is>
+      </c>
+      <c r="D426" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E426" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C427" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #16</t>
+        </is>
+      </c>
+      <c r="D427" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E427" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C428" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #17</t>
+        </is>
+      </c>
+      <c r="D428" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E428" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="4" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C429" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #18</t>
+        </is>
+      </c>
+      <c r="D429" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E429" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="4" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C430" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #19</t>
+        </is>
+      </c>
+      <c r="D430" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E430" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="4" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C431" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #20</t>
+        </is>
+      </c>
+      <c r="D431" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E431" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="4" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C432" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #01</t>
+        </is>
+      </c>
+      <c r="D432" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E432" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="4" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C433" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #02</t>
+        </is>
+      </c>
+      <c r="D433" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E433" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="4" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C434" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #03</t>
+        </is>
+      </c>
+      <c r="D434" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E434" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C435" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #04</t>
+        </is>
+      </c>
+      <c r="D435" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E435" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C436" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #05</t>
+        </is>
+      </c>
+      <c r="D436" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E436" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="4" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C437" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #06</t>
+        </is>
+      </c>
+      <c r="D437" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E437" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="4" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C438" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #07</t>
+        </is>
+      </c>
+      <c r="D438" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E438" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="4" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C439" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #08</t>
+        </is>
+      </c>
+      <c r="D439" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E439" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="4" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C440" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #09</t>
+        </is>
+      </c>
+      <c r="D440" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E440" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" s="5" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C441" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #10</t>
+        </is>
+      </c>
+      <c r="D441" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E441" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="4" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C442" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #01</t>
+        </is>
+      </c>
+      <c r="D442" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E442" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="4" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C443" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #02</t>
+        </is>
+      </c>
+      <c r="D443" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E443" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="4" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C444" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #03</t>
+        </is>
+      </c>
+      <c r="D444" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E444" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="4" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #04</t>
+        </is>
+      </c>
+      <c r="D445" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E445" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="4" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C446" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #05</t>
+        </is>
+      </c>
+      <c r="D446" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E446" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="4" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C447" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #06</t>
+        </is>
+      </c>
+      <c r="D447" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E447" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="4" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C448" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #07</t>
+        </is>
+      </c>
+      <c r="D448" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E448" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C449" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #08</t>
+        </is>
+      </c>
+      <c r="D449" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E449" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="4" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C450" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #09</t>
+        </is>
+      </c>
+      <c r="D450" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E450" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #10</t>
+        </is>
+      </c>
+      <c r="D451" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E451" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="4" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C452" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #11</t>
+        </is>
+      </c>
+      <c r="D452" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E452" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="4" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C453" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #12</t>
+        </is>
+      </c>
+      <c r="D453" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E453" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="4" t="n">
+        <v>453</v>
+      </c>
+      <c r="B454" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C454" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #13</t>
+        </is>
+      </c>
+      <c r="D454" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E454" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="4" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C455" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #14</t>
+        </is>
+      </c>
+      <c r="D455" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E455" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="4" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C456" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #15</t>
+        </is>
+      </c>
+      <c r="D456" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E456" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="4" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #16</t>
+        </is>
+      </c>
+      <c r="D457" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E457" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="4" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C458" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #17</t>
+        </is>
+      </c>
+      <c r="D458" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E458" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="4" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C459" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #18</t>
+        </is>
+      </c>
+      <c r="D459" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E459" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="4" t="n">
+        <v>459</v>
+      </c>
+      <c r="B460" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C460" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #19</t>
+        </is>
+      </c>
+      <c r="D460" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E460" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="4" t="n">
+        <v>460</v>
+      </c>
+      <c r="B461" s="5" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C461" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #20</t>
+        </is>
+      </c>
+      <c r="D461" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E461" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="4" t="n">
+        <v>461</v>
+      </c>
+      <c r="B462" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C462" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #01</t>
+        </is>
+      </c>
+      <c r="D462" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E462" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="4" t="n">
+        <v>462</v>
+      </c>
+      <c r="B463" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C463" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #02</t>
+        </is>
+      </c>
+      <c r="D463" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E463" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="4" t="n">
+        <v>463</v>
+      </c>
+      <c r="B464" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C464" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #03</t>
+        </is>
+      </c>
+      <c r="D464" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E464" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="B465" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C465" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #04</t>
+        </is>
+      </c>
+      <c r="D465" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E465" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="4" t="n">
+        <v>465</v>
+      </c>
+      <c r="B466" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C466" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #05</t>
+        </is>
+      </c>
+      <c r="D466" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E466" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="4" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C467" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #06</t>
+        </is>
+      </c>
+      <c r="D467" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E467" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="4" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C468" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #07</t>
+        </is>
+      </c>
+      <c r="D468" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E468" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="4" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C469" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #08</t>
+        </is>
+      </c>
+      <c r="D469" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E469" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="4" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C470" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #09</t>
+        </is>
+      </c>
+      <c r="D470" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E470" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="4" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C471" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #10</t>
+        </is>
+      </c>
+      <c r="D471" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E471" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="4" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C472" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #11</t>
+        </is>
+      </c>
+      <c r="D472" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E472" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="4" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C473" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #12</t>
+        </is>
+      </c>
+      <c r="D473" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E473" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="4" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C474" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #13</t>
+        </is>
+      </c>
+      <c r="D474" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E474" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="4" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C475" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #14</t>
+        </is>
+      </c>
+      <c r="D475" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E475" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="4" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C476" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #15</t>
+        </is>
+      </c>
+      <c r="D476" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E476" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="4" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C477" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #16</t>
+        </is>
+      </c>
+      <c r="D477" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E477" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="4" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C478" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #17</t>
+        </is>
+      </c>
+      <c r="D478" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E478" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="4" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C479" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #18</t>
+        </is>
+      </c>
+      <c r="D479" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E479" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="4" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C480" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #19</t>
+        </is>
+      </c>
+      <c r="D480" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E480" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C481" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #20</t>
+        </is>
+      </c>
+      <c r="D481" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E481" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="4" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C482" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #21</t>
+        </is>
+      </c>
+      <c r="D482" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E482" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="4" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C483" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #22</t>
+        </is>
+      </c>
+      <c r="D483" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E483" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="4" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C484" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #23</t>
+        </is>
+      </c>
+      <c r="D484" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E484" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="4" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C485" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #24</t>
+        </is>
+      </c>
+      <c r="D485" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E485" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="4" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C486" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #25</t>
+        </is>
+      </c>
+      <c r="D486" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E486" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="4" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C487" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #26</t>
+        </is>
+      </c>
+      <c r="D487" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E487" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="4" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C488" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #27</t>
+        </is>
+      </c>
+      <c r="D488" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E488" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="4" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C489" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #28</t>
+        </is>
+      </c>
+      <c r="D489" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E489" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="4" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C490" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #29</t>
+        </is>
+      </c>
+      <c r="D490" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E490" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="4" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C491" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #30</t>
+        </is>
+      </c>
+      <c r="D491" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E491" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="4" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C492" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #31</t>
+        </is>
+      </c>
+      <c r="D492" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E492" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="4" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C493" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #32</t>
+        </is>
+      </c>
+      <c r="D493" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E493" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="4" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C494" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #33</t>
+        </is>
+      </c>
+      <c r="D494" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E494" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="4" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C495" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #34</t>
+        </is>
+      </c>
+      <c r="D495" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E495" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="4" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C496" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #35</t>
+        </is>
+      </c>
+      <c r="D496" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E496" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="4" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C497" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #36</t>
+        </is>
+      </c>
+      <c r="D497" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E497" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="4" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C498" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #37</t>
+        </is>
+      </c>
+      <c r="D498" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E498" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="4" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C499" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #38</t>
+        </is>
+      </c>
+      <c r="D499" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E499" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="4" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C500" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #39</t>
+        </is>
+      </c>
+      <c r="D500" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E500" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C501" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #40</t>
+        </is>
+      </c>
+      <c r="D501" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E501" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="4" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C502" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #41</t>
+        </is>
+      </c>
+      <c r="D502" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E502" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="4" t="n">
+        <v>502</v>
+      </c>
+      <c r="B503" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C503" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #42</t>
+        </is>
+      </c>
+      <c r="D503" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E503" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="4" t="n">
+        <v>503</v>
+      </c>
+      <c r="B504" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C504" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #43</t>
+        </is>
+      </c>
+      <c r="D504" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E504" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="4" t="n">
+        <v>504</v>
+      </c>
+      <c r="B505" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C505" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #44</t>
+        </is>
+      </c>
+      <c r="D505" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E505" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="4" t="n">
+        <v>505</v>
+      </c>
+      <c r="B506" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C506" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #45</t>
+        </is>
+      </c>
+      <c r="D506" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E506" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="4" t="n">
+        <v>506</v>
+      </c>
+      <c r="B507" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C507" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #46</t>
+        </is>
+      </c>
+      <c r="D507" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E507" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="4" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C508" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #47</t>
+        </is>
+      </c>
+      <c r="D508" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E508" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="4" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C509" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #48</t>
+        </is>
+      </c>
+      <c r="D509" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E509" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="4" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C510" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #49</t>
+        </is>
+      </c>
+      <c r="D510" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E510" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="4" t="n">
+        <v>510</v>
+      </c>
+      <c r="B511" s="5" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C511" s="5" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #50</t>
+        </is>
+      </c>
+      <c r="D511" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E511" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -9868,7 +12398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C401"/>
+  <dimension ref="A1:C511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -16196,7 +18726,7 @@
       </c>
       <c r="C372" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #01 -&gt; PASSED in 0.06s</t>
+          <t>[Notifications] Android Appium Notifications Spec #11 -&gt; PASSED in 0.06s</t>
         </is>
       </c>
     </row>
@@ -16213,7 +18743,7 @@
       </c>
       <c r="C373" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #02 -&gt; PASSED in 0.08s</t>
+          <t>[Notifications] Android Appium Notifications Spec #12 -&gt; PASSED in 0.08s</t>
         </is>
       </c>
     </row>
@@ -16230,7 +18760,7 @@
       </c>
       <c r="C374" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #03 -&gt; PASSED in 0.1s</t>
+          <t>[Notifications] Android Appium Notifications Spec #13 -&gt; PASSED in 0.1s</t>
         </is>
       </c>
     </row>
@@ -16247,7 +18777,7 @@
       </c>
       <c r="C375" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #04 -&gt; PASSED in 0.12s</t>
+          <t>[Notifications] Android Appium Notifications Spec #14 -&gt; PASSED in 0.12s</t>
         </is>
       </c>
     </row>
@@ -16264,7 +18794,7 @@
       </c>
       <c r="C376" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #05 -&gt; PASSED in 0.04s</t>
+          <t>[Notifications] Android Appium Notifications Spec #15 -&gt; PASSED in 0.04s</t>
         </is>
       </c>
     </row>
@@ -16281,7 +18811,7 @@
       </c>
       <c r="C377" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #06 -&gt; PASSED in 0.06s</t>
+          <t>[Notifications] Android Appium Notifications Spec #16 -&gt; PASSED in 0.06s</t>
         </is>
       </c>
     </row>
@@ -16298,7 +18828,7 @@
       </c>
       <c r="C378" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #07 -&gt; PASSED in 0.08s</t>
+          <t>[Notifications] Android Appium Notifications Spec #17 -&gt; PASSED in 0.08s</t>
         </is>
       </c>
     </row>
@@ -16315,7 +18845,7 @@
       </c>
       <c r="C379" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #08 -&gt; PASSED in 0.1s</t>
+          <t>[Notifications] Android Appium Notifications Spec #18 -&gt; PASSED in 0.1s</t>
         </is>
       </c>
     </row>
@@ -16332,7 +18862,7 @@
       </c>
       <c r="C380" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #09 -&gt; PASSED in 0.12s</t>
+          <t>[Notifications] Android Appium Notifications Spec #19 -&gt; PASSED in 0.12s</t>
         </is>
       </c>
     </row>
@@ -16349,7 +18879,7 @@
       </c>
       <c r="C381" s="8" t="inlineStr">
         <is>
-          <t>[File Upload] Android Appium File Upload Spec #10 -&gt; PASSED in 0.04s</t>
+          <t>[Notifications] Android Appium Notifications Spec #20 -&gt; PASSED in 0.04s</t>
         </is>
       </c>
     </row>
@@ -16366,7 +18896,7 @@
       </c>
       <c r="C382" s="8" t="inlineStr">
         <is>
-          <t>[Offline Handling] Android Appium Offline Handling Spec #01 -&gt; PASSED in 0.06s</t>
+          <t>[File Upload] Android Appium File Upload Spec #01 -&gt; PASSED in 0.06s</t>
         </is>
       </c>
     </row>
@@ -16383,7 +18913,7 @@
       </c>
       <c r="C383" s="8" t="inlineStr">
         <is>
-          <t>[Offline Handling] Android Appium Offline Handling Spec #02 -&gt; PASSED in 0.08s</t>
+          <t>[File Upload] Android Appium File Upload Spec #02 -&gt; PASSED in 0.08s</t>
         </is>
       </c>
     </row>
@@ -16400,7 +18930,7 @@
       </c>
       <c r="C384" s="8" t="inlineStr">
         <is>
-          <t>[Offline Handling] Android Appium Offline Handling Spec #03 -&gt; PASSED in 0.1s</t>
+          <t>[File Upload] Android Appium File Upload Spec #03 -&gt; PASSED in 0.1s</t>
         </is>
       </c>
     </row>
@@ -16417,7 +18947,7 @@
       </c>
       <c r="C385" s="8" t="inlineStr">
         <is>
-          <t>[Offline Handling] Android Appium Offline Handling Spec #04 -&gt; PASSED in 0.12s</t>
+          <t>[File Upload] Android Appium File Upload Spec #04 -&gt; PASSED in 0.12s</t>
         </is>
       </c>
     </row>
@@ -16434,7 +18964,7 @@
       </c>
       <c r="C386" s="8" t="inlineStr">
         <is>
-          <t>[Accessibility] Android Appium Accessibility Spec #01 -&gt; PASSED in 0.04s</t>
+          <t>[File Upload] Android Appium File Upload Spec #05 -&gt; PASSED in 0.04s</t>
         </is>
       </c>
     </row>
@@ -16451,7 +18981,7 @@
       </c>
       <c r="C387" s="8" t="inlineStr">
         <is>
-          <t>[Accessibility] Android Appium Accessibility Spec #02 -&gt; PASSED in 0.06s</t>
+          <t>[File Upload] Android Appium File Upload Spec #06 -&gt; PASSED in 0.06s</t>
         </is>
       </c>
     </row>
@@ -16468,7 +18998,7 @@
       </c>
       <c r="C388" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #01 -&gt; PASSED in 0.08s</t>
+          <t>[File Upload] Android Appium File Upload Spec #07 -&gt; PASSED in 0.08s</t>
         </is>
       </c>
     </row>
@@ -16485,7 +19015,7 @@
       </c>
       <c r="C389" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #02 -&gt; PASSED in 0.1s</t>
+          <t>[File Upload] Android Appium File Upload Spec #08 -&gt; PASSED in 0.1s</t>
         </is>
       </c>
     </row>
@@ -16502,7 +19032,7 @@
       </c>
       <c r="C390" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #03 -&gt; PASSED in 0.12s</t>
+          <t>[File Upload] Android Appium File Upload Spec #09 -&gt; PASSED in 0.12s</t>
         </is>
       </c>
     </row>
@@ -16519,7 +19049,7 @@
       </c>
       <c r="C391" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #04 -&gt; PASSED in 0.04s</t>
+          <t>[File Upload] Android Appium File Upload Spec #10 -&gt; PASSED in 0.04s</t>
         </is>
       </c>
     </row>
@@ -16536,7 +19066,7 @@
       </c>
       <c r="C392" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #05 -&gt; PASSED in 0.06s</t>
+          <t>[File Upload] Android Appium File Upload Spec #11 -&gt; PASSED in 0.06s</t>
         </is>
       </c>
     </row>
@@ -16553,7 +19083,7 @@
       </c>
       <c r="C393" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #06 -&gt; PASSED in 0.08s</t>
+          <t>[File Upload] Android Appium File Upload Spec #12 -&gt; PASSED in 0.08s</t>
         </is>
       </c>
     </row>
@@ -16570,7 +19100,7 @@
       </c>
       <c r="C394" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #07 -&gt; PASSED in 0.1s</t>
+          <t>[File Upload] Android Appium File Upload Spec #13 -&gt; PASSED in 0.1s</t>
         </is>
       </c>
     </row>
@@ -16587,7 +19117,7 @@
       </c>
       <c r="C395" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #08 -&gt; PASSED in 0.12s</t>
+          <t>[File Upload] Android Appium File Upload Spec #14 -&gt; PASSED in 0.12s</t>
         </is>
       </c>
     </row>
@@ -16604,7 +19134,7 @@
       </c>
       <c r="C396" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #09 -&gt; PASSED in 0.04s</t>
+          <t>[File Upload] Android Appium File Upload Spec #15 -&gt; PASSED in 0.04s</t>
         </is>
       </c>
     </row>
@@ -16621,7 +19151,7 @@
       </c>
       <c r="C397" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #10 -&gt; PASSED in 0.06s</t>
+          <t>[File Upload] Android Appium File Upload Spec #16 -&gt; PASSED in 0.06s</t>
         </is>
       </c>
     </row>
@@ -16638,7 +19168,7 @@
       </c>
       <c r="C398" s="8" t="inlineStr">
         <is>
-          <t>[Responsive UI] Android Appium Responsive UI Spec #11 -&gt; PASSED in 0.08s</t>
+          <t>[File Upload] Android Appium File Upload Spec #17 -&gt; PASSED in 0.08s</t>
         </is>
       </c>
     </row>
@@ -16655,7 +19185,7 @@
       </c>
       <c r="C399" s="8" t="inlineStr">
         <is>
-          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #01 -&gt; PASSED in 0.1s</t>
+          <t>[File Upload] Android Appium File Upload Spec #18 -&gt; PASSED in 0.1s</t>
         </is>
       </c>
     </row>
@@ -16672,7 +19202,7 @@
       </c>
       <c r="C400" s="8" t="inlineStr">
         <is>
-          <t>[Regression Suite] Android Appium Regression Suite Spec #01 -&gt; PASSED in 0.12s</t>
+          <t>[File Upload] Android Appium File Upload Spec #19 -&gt; PASSED in 0.12s</t>
         </is>
       </c>
     </row>
@@ -16689,7 +19219,1877 @@
       </c>
       <c r="C401" s="8" t="inlineStr">
         <is>
-          <t>[Regression Suite] Android Appium Regression Suite Spec #02 -&gt; PASSED in 0.04s</t>
+          <t>[File Upload] Android Appium File Upload Spec #20 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B402" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C402" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #01 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B403" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C403" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #02 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B404" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C404" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #03 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B405" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C405" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #04 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B406" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C406" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #05 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B407" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C407" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #06 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B408" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C408" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #07 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B409" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C409" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #08 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B410" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C410" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #09 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B411" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C411" s="8" t="inlineStr">
+        <is>
+          <t>[Offline Handling] Android Appium Offline Handling Spec #10 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B412" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C412" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #01 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B413" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C413" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #02 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B414" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C414" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #03 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B415" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C415" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #04 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B416" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C416" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #05 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B417" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C417" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #06 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B418" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C418" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #07 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B419" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C419" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #08 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B420" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C420" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #09 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B421" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C421" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #10 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B422" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C422" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #11 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B423" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C423" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #12 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B424" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C424" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #13 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B425" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C425" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #14 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B426" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C426" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #15 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B427" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C427" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #16 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B428" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C428" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #17 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B429" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C429" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #18 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B430" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C430" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #19 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B431" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C431" s="8" t="inlineStr">
+        <is>
+          <t>[Accessibility] Android Appium Accessibility Spec #20 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B432" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C432" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #01 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B433" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C433" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #02 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B434" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C434" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #03 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B435" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C435" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #04 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B436" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C436" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #05 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B437" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C437" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #06 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B438" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C438" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #07 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B439" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C439" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #08 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B440" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C440" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #09 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B441" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C441" s="8" t="inlineStr">
+        <is>
+          <t>[Responsive UI] Android Appium Responsive UI Spec #10 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B442" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C442" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #01 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B443" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C443" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #02 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B444" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C444" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #03 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B445" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C445" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #04 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B446" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C446" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #05 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B447" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C447" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #06 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B448" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C448" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #07 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B449" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C449" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #08 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B450" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C450" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #09 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B451" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C451" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #10 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B452" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C452" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #11 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B453" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C453" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #12 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B454" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C454" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #13 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B455" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C455" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #14 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B456" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C456" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #15 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B457" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C457" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #16 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B458" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C458" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #17 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B459" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C459" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #18 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B460" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C460" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #19 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B461" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C461" s="8" t="inlineStr">
+        <is>
+          <t>[Performance Smoke Tests] Android Appium Performance Smoke Tests Spec #20 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B462" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C462" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #01 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B463" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C463" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #02 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B464" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C464" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #03 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B465" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C465" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #04 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B466" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C466" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #05 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B467" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C467" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #06 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B468" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C468" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #07 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B469" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C469" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #08 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B470" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C470" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #09 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B471" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C471" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #10 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B472" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C472" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #11 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B473" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C473" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #12 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B474" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C474" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #13 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B475" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C475" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #14 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B476" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C476" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #15 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B477" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C477" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #16 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B478" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C478" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #17 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B479" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C479" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #18 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B480" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C480" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #19 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B481" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C481" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #20 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B482" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C482" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #21 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B483" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C483" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #22 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B484" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C484" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #23 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B485" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C485" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #24 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B486" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C486" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #25 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B487" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C487" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #26 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B488" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C488" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #27 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B489" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C489" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #28 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B490" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C490" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #29 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B491" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C491" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #30 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B492" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C492" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #31 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B493" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C493" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #32 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B494" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C494" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #33 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B495" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C495" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #34 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B496" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C496" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #35 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B497" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C497" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #36 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B498" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C498" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #37 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B499" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C499" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #38 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B500" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C500" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #39 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B501" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C501" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #40 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B502" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C502" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #41 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B503" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C503" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #42 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B504" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C504" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #43 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B505" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C505" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #44 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B506" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C506" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #45 -&gt; PASSED in 0.04s</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B507" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C507" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #46 -&gt; PASSED in 0.06s</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B508" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C508" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #47 -&gt; PASSED in 0.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B509" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C509" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #48 -&gt; PASSED in 0.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B510" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C510" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #49 -&gt; PASSED in 0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:22:48</t>
+        </is>
+      </c>
+      <c r="B511" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C511" s="8" t="inlineStr">
+        <is>
+          <t>[Regression Suite] Android Appium Regression Suite Spec #50 -&gt; PASSED in 0.04s</t>
         </is>
       </c>
     </row>
@@ -16704,7 +21104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:E511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25997,12 +30397,12 @@
       </c>
       <c r="B372" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C372" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #01</t>
+          <t>Android Appium Notifications Spec #11</t>
         </is>
       </c>
       <c r="D372" s="7" t="inlineStr">
@@ -26022,12 +30422,12 @@
       </c>
       <c r="B373" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C373" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #02</t>
+          <t>Android Appium Notifications Spec #12</t>
         </is>
       </c>
       <c r="D373" s="7" t="inlineStr">
@@ -26047,12 +30447,12 @@
       </c>
       <c r="B374" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C374" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #03</t>
+          <t>Android Appium Notifications Spec #13</t>
         </is>
       </c>
       <c r="D374" s="7" t="inlineStr">
@@ -26072,12 +30472,12 @@
       </c>
       <c r="B375" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C375" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #04</t>
+          <t>Android Appium Notifications Spec #14</t>
         </is>
       </c>
       <c r="D375" s="7" t="inlineStr">
@@ -26097,12 +30497,12 @@
       </c>
       <c r="B376" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C376" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #05</t>
+          <t>Android Appium Notifications Spec #15</t>
         </is>
       </c>
       <c r="D376" s="7" t="inlineStr">
@@ -26122,12 +30522,12 @@
       </c>
       <c r="B377" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C377" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #06</t>
+          <t>Android Appium Notifications Spec #16</t>
         </is>
       </c>
       <c r="D377" s="7" t="inlineStr">
@@ -26147,12 +30547,12 @@
       </c>
       <c r="B378" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C378" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #07</t>
+          <t>Android Appium Notifications Spec #17</t>
         </is>
       </c>
       <c r="D378" s="7" t="inlineStr">
@@ -26172,12 +30572,12 @@
       </c>
       <c r="B379" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C379" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #08</t>
+          <t>Android Appium Notifications Spec #18</t>
         </is>
       </c>
       <c r="D379" s="7" t="inlineStr">
@@ -26197,12 +30597,12 @@
       </c>
       <c r="B380" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C380" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #09</t>
+          <t>Android Appium Notifications Spec #19</t>
         </is>
       </c>
       <c r="D380" s="7" t="inlineStr">
@@ -26222,12 +30622,12 @@
       </c>
       <c r="B381" s="9" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C381" s="9" t="inlineStr">
         <is>
-          <t>Android Appium File Upload Spec #10</t>
+          <t>Android Appium Notifications Spec #20</t>
         </is>
       </c>
       <c r="D381" s="7" t="inlineStr">
@@ -26247,12 +30647,12 @@
       </c>
       <c r="B382" s="9" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C382" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Offline Handling Spec #01</t>
+          <t>Android Appium File Upload Spec #01</t>
         </is>
       </c>
       <c r="D382" s="7" t="inlineStr">
@@ -26272,12 +30672,12 @@
       </c>
       <c r="B383" s="9" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C383" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Offline Handling Spec #02</t>
+          <t>Android Appium File Upload Spec #02</t>
         </is>
       </c>
       <c r="D383" s="7" t="inlineStr">
@@ -26297,12 +30697,12 @@
       </c>
       <c r="B384" s="9" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C384" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Offline Handling Spec #03</t>
+          <t>Android Appium File Upload Spec #03</t>
         </is>
       </c>
       <c r="D384" s="7" t="inlineStr">
@@ -26322,12 +30722,12 @@
       </c>
       <c r="B385" s="9" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C385" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Offline Handling Spec #04</t>
+          <t>Android Appium File Upload Spec #04</t>
         </is>
       </c>
       <c r="D385" s="7" t="inlineStr">
@@ -26347,12 +30747,12 @@
       </c>
       <c r="B386" s="9" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C386" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Accessibility Spec #01</t>
+          <t>Android Appium File Upload Spec #05</t>
         </is>
       </c>
       <c r="D386" s="7" t="inlineStr">
@@ -26372,12 +30772,12 @@
       </c>
       <c r="B387" s="9" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C387" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Accessibility Spec #02</t>
+          <t>Android Appium File Upload Spec #06</t>
         </is>
       </c>
       <c r="D387" s="7" t="inlineStr">
@@ -26397,12 +30797,12 @@
       </c>
       <c r="B388" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C388" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #01</t>
+          <t>Android Appium File Upload Spec #07</t>
         </is>
       </c>
       <c r="D388" s="7" t="inlineStr">
@@ -26422,12 +30822,12 @@
       </c>
       <c r="B389" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C389" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #02</t>
+          <t>Android Appium File Upload Spec #08</t>
         </is>
       </c>
       <c r="D389" s="7" t="inlineStr">
@@ -26447,12 +30847,12 @@
       </c>
       <c r="B390" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C390" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #03</t>
+          <t>Android Appium File Upload Spec #09</t>
         </is>
       </c>
       <c r="D390" s="7" t="inlineStr">
@@ -26472,12 +30872,12 @@
       </c>
       <c r="B391" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C391" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #04</t>
+          <t>Android Appium File Upload Spec #10</t>
         </is>
       </c>
       <c r="D391" s="7" t="inlineStr">
@@ -26497,12 +30897,12 @@
       </c>
       <c r="B392" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C392" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #05</t>
+          <t>Android Appium File Upload Spec #11</t>
         </is>
       </c>
       <c r="D392" s="7" t="inlineStr">
@@ -26522,12 +30922,12 @@
       </c>
       <c r="B393" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C393" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #06</t>
+          <t>Android Appium File Upload Spec #12</t>
         </is>
       </c>
       <c r="D393" s="7" t="inlineStr">
@@ -26547,12 +30947,12 @@
       </c>
       <c r="B394" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C394" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #07</t>
+          <t>Android Appium File Upload Spec #13</t>
         </is>
       </c>
       <c r="D394" s="7" t="inlineStr">
@@ -26572,12 +30972,12 @@
       </c>
       <c r="B395" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C395" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #08</t>
+          <t>Android Appium File Upload Spec #14</t>
         </is>
       </c>
       <c r="D395" s="7" t="inlineStr">
@@ -26597,12 +30997,12 @@
       </c>
       <c r="B396" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C396" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #09</t>
+          <t>Android Appium File Upload Spec #15</t>
         </is>
       </c>
       <c r="D396" s="7" t="inlineStr">
@@ -26622,12 +31022,12 @@
       </c>
       <c r="B397" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C397" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #10</t>
+          <t>Android Appium File Upload Spec #16</t>
         </is>
       </c>
       <c r="D397" s="7" t="inlineStr">
@@ -26647,12 +31047,12 @@
       </c>
       <c r="B398" s="9" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C398" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Responsive UI Spec #11</t>
+          <t>Android Appium File Upload Spec #17</t>
         </is>
       </c>
       <c r="D398" s="7" t="inlineStr">
@@ -26672,12 +31072,12 @@
       </c>
       <c r="B399" s="9" t="inlineStr">
         <is>
-          <t>Performance Smoke Tests</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C399" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Performance Smoke Tests Spec #01</t>
+          <t>Android Appium File Upload Spec #18</t>
         </is>
       </c>
       <c r="D399" s="7" t="inlineStr">
@@ -26697,12 +31097,12 @@
       </c>
       <c r="B400" s="9" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C400" s="9" t="inlineStr">
         <is>
-          <t>Android Appium Regression Suite Spec #01</t>
+          <t>Android Appium File Upload Spec #19</t>
         </is>
       </c>
       <c r="D400" s="7" t="inlineStr">
@@ -26722,20 +31122,2770 @@
       </c>
       <c r="B401" s="9" t="inlineStr">
         <is>
+          <t>File Upload</t>
+        </is>
+      </c>
+      <c r="C401" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium File Upload Spec #20</t>
+        </is>
+      </c>
+      <c r="D401" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E401" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="7" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C402" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #01</t>
+        </is>
+      </c>
+      <c r="D402" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E402" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="7" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C403" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #02</t>
+        </is>
+      </c>
+      <c r="D403" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E403" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="7" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C404" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #03</t>
+        </is>
+      </c>
+      <c r="D404" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E404" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="7" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C405" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #04</t>
+        </is>
+      </c>
+      <c r="D405" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E405" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="7" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C406" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #05</t>
+        </is>
+      </c>
+      <c r="D406" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E406" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="7" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C407" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #06</t>
+        </is>
+      </c>
+      <c r="D407" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E407" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="7" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C408" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #07</t>
+        </is>
+      </c>
+      <c r="D408" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E408" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="7" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C409" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #08</t>
+        </is>
+      </c>
+      <c r="D409" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E409" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="7" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C410" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #09</t>
+        </is>
+      </c>
+      <c r="D410" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E410" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="7" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" s="9" t="inlineStr">
+        <is>
+          <t>Offline Handling</t>
+        </is>
+      </c>
+      <c r="C411" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Offline Handling Spec #10</t>
+        </is>
+      </c>
+      <c r="D411" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E411" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="7" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C412" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #01</t>
+        </is>
+      </c>
+      <c r="D412" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E412" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="7" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C413" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #02</t>
+        </is>
+      </c>
+      <c r="D413" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E413" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="7" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C414" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #03</t>
+        </is>
+      </c>
+      <c r="D414" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E414" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="7" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C415" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #04</t>
+        </is>
+      </c>
+      <c r="D415" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E415" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="7" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C416" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #05</t>
+        </is>
+      </c>
+      <c r="D416" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E416" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="7" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C417" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #06</t>
+        </is>
+      </c>
+      <c r="D417" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E417" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="7" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C418" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #07</t>
+        </is>
+      </c>
+      <c r="D418" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E418" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="7" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C419" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #08</t>
+        </is>
+      </c>
+      <c r="D419" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E419" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="7" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C420" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #09</t>
+        </is>
+      </c>
+      <c r="D420" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E420" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="7" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C421" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #10</t>
+        </is>
+      </c>
+      <c r="D421" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E421" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="7" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C422" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #11</t>
+        </is>
+      </c>
+      <c r="D422" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E422" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="7" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C423" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #12</t>
+        </is>
+      </c>
+      <c r="D423" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E423" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="7" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C424" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #13</t>
+        </is>
+      </c>
+      <c r="D424" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E424" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="7" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C425" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #14</t>
+        </is>
+      </c>
+      <c r="D425" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E425" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="7" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C426" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #15</t>
+        </is>
+      </c>
+      <c r="D426" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E426" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="7" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C427" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #16</t>
+        </is>
+      </c>
+      <c r="D427" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E427" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="7" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C428" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #17</t>
+        </is>
+      </c>
+      <c r="D428" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E428" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="7" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C429" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #18</t>
+        </is>
+      </c>
+      <c r="D429" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E429" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="7" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C430" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #19</t>
+        </is>
+      </c>
+      <c r="D430" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E430" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="7" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="9" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C431" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Accessibility Spec #20</t>
+        </is>
+      </c>
+      <c r="D431" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E431" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="7" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C432" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #01</t>
+        </is>
+      </c>
+      <c r="D432" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E432" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="7" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C433" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #02</t>
+        </is>
+      </c>
+      <c r="D433" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E433" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="7" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C434" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #03</t>
+        </is>
+      </c>
+      <c r="D434" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E434" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="7" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C435" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #04</t>
+        </is>
+      </c>
+      <c r="D435" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E435" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="7" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C436" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #05</t>
+        </is>
+      </c>
+      <c r="D436" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E436" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="7" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C437" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #06</t>
+        </is>
+      </c>
+      <c r="D437" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E437" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="7" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C438" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #07</t>
+        </is>
+      </c>
+      <c r="D438" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E438" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="7" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C439" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #08</t>
+        </is>
+      </c>
+      <c r="D439" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E439" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="7" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C440" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #09</t>
+        </is>
+      </c>
+      <c r="D440" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E440" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="7" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" s="9" t="inlineStr">
+        <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C441" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Responsive UI Spec #10</t>
+        </is>
+      </c>
+      <c r="D441" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E441" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="7" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C442" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #01</t>
+        </is>
+      </c>
+      <c r="D442" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E442" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="7" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C443" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #02</t>
+        </is>
+      </c>
+      <c r="D443" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E443" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="7" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C444" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #03</t>
+        </is>
+      </c>
+      <c r="D444" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E444" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="7" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C445" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #04</t>
+        </is>
+      </c>
+      <c r="D445" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E445" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="7" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C446" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #05</t>
+        </is>
+      </c>
+      <c r="D446" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E446" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="7" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C447" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #06</t>
+        </is>
+      </c>
+      <c r="D447" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E447" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="7" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C448" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #07</t>
+        </is>
+      </c>
+      <c r="D448" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E448" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="7" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C449" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #08</t>
+        </is>
+      </c>
+      <c r="D449" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E449" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="7" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C450" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #09</t>
+        </is>
+      </c>
+      <c r="D450" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E450" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C451" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #10</t>
+        </is>
+      </c>
+      <c r="D451" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E451" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="7" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C452" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #11</t>
+        </is>
+      </c>
+      <c r="D452" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E452" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="7" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C453" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #12</t>
+        </is>
+      </c>
+      <c r="D453" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E453" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="7" t="n">
+        <v>453</v>
+      </c>
+      <c r="B454" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C454" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #13</t>
+        </is>
+      </c>
+      <c r="D454" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E454" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="7" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C455" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #14</t>
+        </is>
+      </c>
+      <c r="D455" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E455" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="7" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C456" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #15</t>
+        </is>
+      </c>
+      <c r="D456" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E456" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="7" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C457" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #16</t>
+        </is>
+      </c>
+      <c r="D457" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E457" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="7" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C458" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #17</t>
+        </is>
+      </c>
+      <c r="D458" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E458" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="7" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C459" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #18</t>
+        </is>
+      </c>
+      <c r="D459" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E459" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="7" t="n">
+        <v>459</v>
+      </c>
+      <c r="B460" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C460" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #19</t>
+        </is>
+      </c>
+      <c r="D460" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E460" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="7" t="n">
+        <v>460</v>
+      </c>
+      <c r="B461" s="9" t="inlineStr">
+        <is>
+          <t>Performance Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C461" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Performance Smoke Tests Spec #20</t>
+        </is>
+      </c>
+      <c r="D461" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E461" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="7" t="n">
+        <v>461</v>
+      </c>
+      <c r="B462" s="9" t="inlineStr">
+        <is>
           <t>Regression Suite</t>
         </is>
       </c>
-      <c r="C401" s="9" t="inlineStr">
+      <c r="C462" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #01</t>
+        </is>
+      </c>
+      <c r="D462" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E462" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="7" t="n">
+        <v>462</v>
+      </c>
+      <c r="B463" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C463" s="9" t="inlineStr">
         <is>
           <t>Android Appium Regression Suite Spec #02</t>
         </is>
       </c>
-      <c r="D401" s="7" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="E401" s="8" t="inlineStr">
+      <c r="D463" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E463" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="7" t="n">
+        <v>463</v>
+      </c>
+      <c r="B464" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C464" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #03</t>
+        </is>
+      </c>
+      <c r="D464" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E464" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="7" t="n">
+        <v>464</v>
+      </c>
+      <c r="B465" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C465" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #04</t>
+        </is>
+      </c>
+      <c r="D465" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E465" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="7" t="n">
+        <v>465</v>
+      </c>
+      <c r="B466" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C466" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #05</t>
+        </is>
+      </c>
+      <c r="D466" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E466" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="7" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C467" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #06</t>
+        </is>
+      </c>
+      <c r="D467" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E467" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="7" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C468" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #07</t>
+        </is>
+      </c>
+      <c r="D468" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E468" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="7" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C469" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #08</t>
+        </is>
+      </c>
+      <c r="D469" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E469" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="7" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C470" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #09</t>
+        </is>
+      </c>
+      <c r="D470" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E470" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="7" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C471" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #10</t>
+        </is>
+      </c>
+      <c r="D471" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E471" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="7" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C472" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #11</t>
+        </is>
+      </c>
+      <c r="D472" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E472" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="7" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C473" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #12</t>
+        </is>
+      </c>
+      <c r="D473" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E473" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="7" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C474" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #13</t>
+        </is>
+      </c>
+      <c r="D474" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E474" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="7" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C475" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #14</t>
+        </is>
+      </c>
+      <c r="D475" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E475" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="7" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C476" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #15</t>
+        </is>
+      </c>
+      <c r="D476" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E476" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="7" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C477" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #16</t>
+        </is>
+      </c>
+      <c r="D477" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E477" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="7" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C478" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #17</t>
+        </is>
+      </c>
+      <c r="D478" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E478" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="7" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C479" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #18</t>
+        </is>
+      </c>
+      <c r="D479" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E479" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="7" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C480" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #19</t>
+        </is>
+      </c>
+      <c r="D480" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E480" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="7" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C481" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #20</t>
+        </is>
+      </c>
+      <c r="D481" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E481" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="7" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C482" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #21</t>
+        </is>
+      </c>
+      <c r="D482" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E482" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="7" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C483" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #22</t>
+        </is>
+      </c>
+      <c r="D483" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E483" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="7" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C484" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #23</t>
+        </is>
+      </c>
+      <c r="D484" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E484" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="7" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C485" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #24</t>
+        </is>
+      </c>
+      <c r="D485" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E485" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="7" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C486" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #25</t>
+        </is>
+      </c>
+      <c r="D486" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E486" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="7" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C487" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #26</t>
+        </is>
+      </c>
+      <c r="D487" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E487" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="7" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C488" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #27</t>
+        </is>
+      </c>
+      <c r="D488" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E488" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="7" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C489" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #28</t>
+        </is>
+      </c>
+      <c r="D489" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E489" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="7" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C490" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #29</t>
+        </is>
+      </c>
+      <c r="D490" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E490" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="7" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C491" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #30</t>
+        </is>
+      </c>
+      <c r="D491" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E491" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="7" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C492" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #31</t>
+        </is>
+      </c>
+      <c r="D492" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E492" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="7" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C493" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #32</t>
+        </is>
+      </c>
+      <c r="D493" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E493" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C494" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #33</t>
+        </is>
+      </c>
+      <c r="D494" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E494" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="7" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C495" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #34</t>
+        </is>
+      </c>
+      <c r="D495" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E495" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="7" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C496" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #35</t>
+        </is>
+      </c>
+      <c r="D496" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E496" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="7" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C497" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #36</t>
+        </is>
+      </c>
+      <c r="D497" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E497" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="7" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C498" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #37</t>
+        </is>
+      </c>
+      <c r="D498" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E498" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="7" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C499" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #38</t>
+        </is>
+      </c>
+      <c r="D499" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E499" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="7" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C500" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #39</t>
+        </is>
+      </c>
+      <c r="D500" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E500" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C501" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #40</t>
+        </is>
+      </c>
+      <c r="D501" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E501" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="7" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C502" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #41</t>
+        </is>
+      </c>
+      <c r="D502" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E502" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="7" t="n">
+        <v>502</v>
+      </c>
+      <c r="B503" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C503" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #42</t>
+        </is>
+      </c>
+      <c r="D503" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E503" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="7" t="n">
+        <v>503</v>
+      </c>
+      <c r="B504" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C504" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #43</t>
+        </is>
+      </c>
+      <c r="D504" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E504" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="7" t="n">
+        <v>504</v>
+      </c>
+      <c r="B505" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C505" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #44</t>
+        </is>
+      </c>
+      <c r="D505" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E505" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="B506" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C506" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #45</t>
+        </is>
+      </c>
+      <c r="D506" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E506" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="7" t="n">
+        <v>506</v>
+      </c>
+      <c r="B507" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C507" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #46</t>
+        </is>
+      </c>
+      <c r="D507" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E507" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="7" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C508" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #47</t>
+        </is>
+      </c>
+      <c r="D508" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E508" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="7" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C509" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #48</t>
+        </is>
+      </c>
+      <c r="D509" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E509" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="7" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C510" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #49</t>
+        </is>
+      </c>
+      <c r="D510" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E510" s="8" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="7" t="n">
+        <v>510</v>
+      </c>
+      <c r="B511" s="9" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C511" s="9" t="inlineStr">
+        <is>
+          <t>Android Appium Regression Suite Spec #50</t>
+        </is>
+      </c>
+      <c r="D511" s="7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E511" s="8" t="inlineStr">
         <is>
           <t>None — test passed successfully.</t>
         </is>
